--- a/光伏配储项目/电价数据/2026/鼎安电厂.xlsx
+++ b/光伏配储项目/电价数据/2026/鼎安电厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50981</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.82482</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.61715</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.63059</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51877</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50248</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43747</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42299</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42061</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44369</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25612</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12021</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09773</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10811</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09426000000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11881</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.50443</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.40386</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.10958</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09032999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.17788</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>1.00602</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7574</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22085</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.10856</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.65738</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.64439</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.9441900000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27223</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>1.14565</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.9735499999999999</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19132</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.14612</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.13353</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.62751</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.53137</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.8149400000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.76112</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.67367</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5729299999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45902</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6144299999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.80662</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.67043</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.62291</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.75513</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.96612</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.5335599999999999</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6725399999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5733200000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7219500000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.55598</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.5389700000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6392899999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.61166</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4719100000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47688</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41598</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42564</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69553</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.37504</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7262799999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.14354</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.76842</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5216900000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51885</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50518</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50844</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48946</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46998</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41934</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5920599999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.66026</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43017</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5125700000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.52549</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.05422</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>1.2803</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>1.33017</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.28619</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>1.22347</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>1.11707</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.9308999999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.67711</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7152000000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.79802</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.40393</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.43009</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.44435</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1.76248</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.49472</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.12733</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>1.23464</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>1.11517</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4897</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.52983</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.2605</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.99285</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.02165</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5628200000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.68571</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.55625</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6902999999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7356</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.72941</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.5485599999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.50944</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.74553</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.51747</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.23745</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.35912</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.97463</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.29652</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>1.01436</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.65044</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.6417200000000001</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.8863799999999999</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>1.05618</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.49675</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.44218</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33456</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1.24021</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.46367</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.5077900000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.55322</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.5691</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.52842</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.6416900000000001</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6832</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.47818</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.47278</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.67537</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.66859</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.5458200000000001</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.47147</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.42126</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20358</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26675</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47405</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.55064</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52132</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48417</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.15908</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.26745</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.48272</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5325299999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.61349</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.60337</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.79498</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45836</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.49155</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44659</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46019</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44645</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34237</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.72012</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.6024299999999999</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.22616</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22325</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.71996</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.34125</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.31552</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.71351</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.24771</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.60521</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.24502</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.43175</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.07385</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.08027</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1.24812</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.7082999999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.72654</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06354</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.56543</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.24745</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.25898</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.23585</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14654</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42037</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.56529</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46778</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.46649</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.56145</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.63467</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7446900000000001</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.6626799999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.49382</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.61607</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29848</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.17588</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-0.04261</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.16583</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.16214</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.12551</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.17716</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.15919</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.12232</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.12358</v>
+      </c>
+      <c r="R121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.18665</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.19823</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.19823</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.20156</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.19554</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.03664</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>-0.00543</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.16241</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.2770899999999999</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.24686</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.21261</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.20933</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.21266</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.18873</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.23235</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.49043</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25979</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.16753</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.20149</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.15987</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.17404</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.17011</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16676</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.20611</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.21799</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20937</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.16081</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>-0.01956</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.07604999999999999</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.14128</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.14002</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.23803</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.21868</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.17466</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.17463</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.16189</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.18942</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.17959</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.17404</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.7117100000000001</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.19101</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.14592</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.15914</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.14449</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.12532</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.12607</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.13465</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.13341</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.12679</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.11734</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.11586</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.12679</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.02269</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.08909</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.10879</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.07457</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.15784</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.13624</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.18836</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.16232</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.12679</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.22403</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.21456</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.22432</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.19141</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.18028</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.17579</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.18055</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.22517</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.18746</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.24401</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.2029</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.26212</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.23074</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.14054</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.15813</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.15939</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.18887</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.19038</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.16547</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.22318</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.60534</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.44657</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.7260700000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.79683</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.07411</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0.98391</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.6891699999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.50935</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.11569</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0.84037</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.48196</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.6222000000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.44221</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.08376</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.00301</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.26882</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.45691</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.6865</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.66952</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.65424</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.68121</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.21619</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.1985</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.19961</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.17579</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.21057</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.23872</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.22432</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.18028</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.17621</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.23527</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.24019</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.24082</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.25871</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.18773</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.18836</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.2108</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.18477</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.18477</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.18953</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.16223</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.13433</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.18297</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.02022</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.18477</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.09018000000000001</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.15602</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.18773</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.21619</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.20811</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.20544</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.19823</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.20452</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.20272</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.27454</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.19477</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.19105</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.22498</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.1262</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.12899</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.16609</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.22397</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.27041</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.13257</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.15055</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.19983</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.19105</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.43277</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.22517</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.25348</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.20991</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.22068</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.22517</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.22966</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.18773</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.18504</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.20233</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.20537</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.21619</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.18477</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.25274</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.23569</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.11583</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.15365</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.17389</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.17489</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.18324</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.15364</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.11816</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.05009</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.12267</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.04118</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.23284</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.15096</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.18005</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.14839</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.16817</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.25508</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.23114</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.17391</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.25085</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.25587</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25559</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.26411</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.17858</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.07790999999999999</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.21893</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.4376</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.21619</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.69835</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.10745</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.49941</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.27433</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.25228</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.25756</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.23329</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.18349</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.20239</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.20029</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.14911</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.20163</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>-0.00315</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.00377</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.00827</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.06469</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-0.00215</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.06246</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.00087</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.15831</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.16015</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.18349</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.20791</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.23799</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.19529</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.22569</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.20981</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.16022</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.17222</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.16913</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.16393</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.17849</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.18784</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.18349</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.17477</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.16455</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.16882</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.16753</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.16696</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.15316</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.16875</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.16908</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.16316</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.18566</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.16142</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.15344</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.16762</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.15438</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.15806</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.16321</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.22832</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.16941</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.21105</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.2157</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.18068</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.17439</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.16469</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.20452</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.17664</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.15484</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.08778</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.06570000000000001</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.09668</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.09813</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.05528</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.07329000000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.03496</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.04577000000000001</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.13765</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.17105</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.18242</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.20228</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.16727</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.20781</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.20259</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.18669</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.18962</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.23792</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.2239</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.25643</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.23829</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.23291</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.20315</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.18717</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.25528</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.24312</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.22506</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.20721</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.15698</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.15849</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.07726000000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.12567</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21071</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.15567</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.25755</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.21771</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.13153</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.16684</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24265</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.20537</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.26709</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.27554</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.15321</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.20526</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.14129</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42319</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30012</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.59334</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.56023</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43221</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.58914</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.55155</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25054</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.11477</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.64523</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22393</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.63761</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45523</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7024199999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5039399999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25908</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28882</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.35574</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.03836999999999999</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.19491</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.19578</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.19447</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.19375</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40869</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6335700000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8113400000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3406</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19865</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25538</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22195</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26773</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48608</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.77654</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5790700000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.86839</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.62254</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.70075</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.7109800000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.87027</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44297</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48876</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47635</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37753</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49228</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.50932</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46841</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.46841</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42136</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40613</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40636</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42214</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.46273</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45389</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5786100000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.51803</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.46297</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46366</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44776</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.48765</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46838</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.58488</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.45471</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.59233</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15036</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.27279</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.50432</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44787</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.52842</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.49837</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.7253500000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.80308</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.68372</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.69782</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80448</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5703400000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50988</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.78565</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.72888</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6205900000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65412</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.46991</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47335</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46127</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5465399999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45307</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20989</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46692</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46056</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11284</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17726</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27422</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22752</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23039</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25031</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25804</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14668</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25124</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25119</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16965</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.17089</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22813</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.28501</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.352</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26761</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.18204</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.22874</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23691</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.12264</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.00434</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02773</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02757</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03985</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.11136</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.0007199999999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04977</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02867</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04138</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19327</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2199</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25385</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.20896</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.68289</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.50534</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28096</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.26673</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26779</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.2414</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.73045</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.74576</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.72711</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.68238</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.21138</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.25787</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.22941</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.18667</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.18694</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.15749</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.11528</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.15832</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01779</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.18445</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.18483</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.19535</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.00859</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.16637</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.16909</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.17072</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.20517</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.325</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.1196</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5373600000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41599</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14864</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.43527</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32834</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.56123</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.54261</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.48386</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.25386</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27844</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48727</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.49683</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.43163</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46399</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41703</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.42804</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36701</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47621</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.44468</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49057</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56925</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56837</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.41036</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.49139</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.57223</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.48726</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5334500000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5143799999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.56108</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5812200000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.66098</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7268600000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54995</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.54898</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44036</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37377</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27907</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.13684</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.2376</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.21801</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13767</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19335</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16288</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15058</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.04348</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.05111</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.1494</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06616</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18158</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.14115</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16672</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.27804</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>1.31316</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>1.30579</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37747</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.92723</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.50231</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45627</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41436</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39412</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.12955</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.2074</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16025</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.17119</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.28711</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.31287</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.27834</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.32563</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.46872</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.52643</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.26635</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.24484</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.26972</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13388</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.17978</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.10599</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08804000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02895</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.1116</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.20498</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.14157</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.27269</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.14357</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05102</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.17797</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.13482</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.22231</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.28653</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.23961</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45489</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37514</v>
       </c>
     </row>
   </sheetData>
